--- a/artfynd/A 40958-2024 artfynd.xlsx
+++ b/artfynd/A 40958-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072466</v>
+        <v>121072464</v>
       </c>
       <c r="B2" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545730</v>
+        <v>545721</v>
       </c>
       <c r="R2" t="n">
-        <v>7205418</v>
+        <v>7205402</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>121072460</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072470</v>
+        <v>121072465</v>
       </c>
       <c r="B4" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545714</v>
+        <v>545720</v>
       </c>
       <c r="R4" t="n">
-        <v>7205452</v>
+        <v>7205402</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>121072459</v>
       </c>
       <c r="B5" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>121072455</v>
       </c>
       <c r="B6" t="n">
-        <v>79715</v>
+        <v>79718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072451</v>
+        <v>121072469</v>
       </c>
       <c r="B7" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545599</v>
+        <v>545736</v>
       </c>
       <c r="R7" t="n">
-        <v>7205293</v>
+        <v>7205415</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072479</v>
+        <v>121072475</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545732</v>
+        <v>545745</v>
       </c>
       <c r="R8" t="n">
-        <v>7205572</v>
+        <v>7205479</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072467</v>
+        <v>121072466</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072458</v>
+        <v>121072468</v>
       </c>
       <c r="B10" t="n">
-        <v>79715</v>
+        <v>79717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545708</v>
+        <v>545731</v>
       </c>
       <c r="R10" t="n">
-        <v>7205391</v>
+        <v>7205418</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072452</v>
+        <v>121072449</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>56555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1699,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545599</v>
+        <v>545556</v>
       </c>
       <c r="R11" t="n">
-        <v>7205293</v>
+        <v>7205352</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072461</v>
+        <v>121072479</v>
       </c>
       <c r="B12" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545722</v>
+        <v>545732</v>
       </c>
       <c r="R12" t="n">
-        <v>7205383</v>
+        <v>7205572</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072473</v>
+        <v>121072463</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545728</v>
+        <v>545721</v>
       </c>
       <c r="R13" t="n">
-        <v>7205466</v>
+        <v>7205404</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072462</v>
+        <v>121072473</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545722</v>
+        <v>545728</v>
       </c>
       <c r="R14" t="n">
-        <v>7205383</v>
+        <v>7205466</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072477</v>
+        <v>121072458</v>
       </c>
       <c r="B15" t="n">
-        <v>74705</v>
+        <v>79718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545733</v>
+        <v>545708</v>
       </c>
       <c r="R15" t="n">
-        <v>7205544</v>
+        <v>7205391</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072474</v>
+        <v>121072471</v>
       </c>
       <c r="B16" t="n">
-        <v>90701</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2268,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545747</v>
+        <v>545706</v>
       </c>
       <c r="R16" t="n">
-        <v>7205478</v>
+        <v>7205465</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072471</v>
+        <v>121072448</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545706</v>
+        <v>545544</v>
       </c>
       <c r="R17" t="n">
-        <v>7205465</v>
+        <v>7205290</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072468</v>
+        <v>121072456</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,20 +2488,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2507,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545731</v>
+        <v>545699</v>
       </c>
       <c r="R18" t="n">
-        <v>7205418</v>
+        <v>7205364</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072463</v>
+        <v>121072447</v>
       </c>
       <c r="B19" t="n">
-        <v>79715</v>
+        <v>79683</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2600,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545721</v>
+        <v>545544</v>
       </c>
       <c r="R19" t="n">
-        <v>7205404</v>
+        <v>7205293</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072472</v>
+        <v>121072474</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>90711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2712,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545728</v>
+        <v>545747</v>
       </c>
       <c r="R20" t="n">
-        <v>7205466</v>
+        <v>7205478</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072447</v>
+        <v>121072467</v>
       </c>
       <c r="B21" t="n">
-        <v>79680</v>
+        <v>79711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2824,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545544</v>
+        <v>545730</v>
       </c>
       <c r="R21" t="n">
-        <v>7205293</v>
+        <v>7205418</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072449</v>
+        <v>121072478</v>
       </c>
       <c r="B22" t="n">
-        <v>56552</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,43 +2940,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545556</v>
+        <v>545728</v>
       </c>
       <c r="R22" t="n">
-        <v>7205352</v>
+        <v>7205539</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,7 +3039,7 @@
         <v>121072453</v>
       </c>
       <c r="B23" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072465</v>
+        <v>121072451</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545720</v>
+        <v>545599</v>
       </c>
       <c r="R24" t="n">
-        <v>7205402</v>
+        <v>7205293</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072464</v>
+        <v>121072454</v>
       </c>
       <c r="B25" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545721</v>
+        <v>545691</v>
       </c>
       <c r="R25" t="n">
-        <v>7205402</v>
+        <v>7205351</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072456</v>
+        <v>121072457</v>
       </c>
       <c r="B26" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545699</v>
+        <v>545695</v>
       </c>
       <c r="R26" t="n">
-        <v>7205364</v>
+        <v>7205372</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072448</v>
+        <v>121072461</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545544</v>
+        <v>545722</v>
       </c>
       <c r="R27" t="n">
-        <v>7205290</v>
+        <v>7205383</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072454</v>
+        <v>121072476</v>
       </c>
       <c r="B28" t="n">
-        <v>79680</v>
+        <v>94484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,25 +3613,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545691</v>
+        <v>545729</v>
       </c>
       <c r="R28" t="n">
-        <v>7205351</v>
+        <v>7205541</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3713,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072476</v>
+        <v>121072472</v>
       </c>
       <c r="B29" t="n">
-        <v>94474</v>
+        <v>79711</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,21 +3729,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545729</v>
+        <v>545728</v>
       </c>
       <c r="R29" t="n">
-        <v>7205541</v>
+        <v>7205466</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072478</v>
+        <v>121072477</v>
       </c>
       <c r="B30" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,21 +3841,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545728</v>
+        <v>545733</v>
       </c>
       <c r="R30" t="n">
-        <v>7205539</v>
+        <v>7205544</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3937,10 +3937,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072469</v>
+        <v>121072470</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,25 +3949,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545736</v>
+        <v>545714</v>
       </c>
       <c r="R31" t="n">
-        <v>7205415</v>
+        <v>7205452</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,10 +4049,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072457</v>
+        <v>121072462</v>
       </c>
       <c r="B32" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545695</v>
+        <v>545722</v>
       </c>
       <c r="R32" t="n">
-        <v>7205372</v>
+        <v>7205383</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072475</v>
+        <v>121072452</v>
       </c>
       <c r="B33" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545745</v>
+        <v>545599</v>
       </c>
       <c r="R33" t="n">
-        <v>7205479</v>
+        <v>7205293</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 40958-2024 artfynd.xlsx
+++ b/artfynd/A 40958-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072464</v>
+        <v>121072460</v>
       </c>
       <c r="B2" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545721</v>
+        <v>545707</v>
       </c>
       <c r="R2" t="n">
-        <v>7205402</v>
+        <v>7205394</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072460</v>
+        <v>121072464</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545707</v>
+        <v>545721</v>
       </c>
       <c r="R3" t="n">
-        <v>7205394</v>
+        <v>7205402</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072475</v>
+        <v>121072468</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>79717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,20 +1359,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545745</v>
+        <v>545731</v>
       </c>
       <c r="R8" t="n">
-        <v>7205479</v>
+        <v>7205418</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072466</v>
+        <v>121072475</v>
       </c>
       <c r="B9" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545730</v>
+        <v>545745</v>
       </c>
       <c r="R9" t="n">
-        <v>7205418</v>
+        <v>7205479</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072468</v>
+        <v>121072466</v>
       </c>
       <c r="B10" t="n">
-        <v>79717</v>
+        <v>79683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545731</v>
+        <v>545730</v>
       </c>
       <c r="R10" t="n">
         <v>7205418</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072476</v>
+        <v>121072472</v>
       </c>
       <c r="B28" t="n">
-        <v>94484</v>
+        <v>79711</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545729</v>
+        <v>545728</v>
       </c>
       <c r="R28" t="n">
-        <v>7205541</v>
+        <v>7205466</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3713,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072472</v>
+        <v>121072477</v>
       </c>
       <c r="B29" t="n">
-        <v>79711</v>
+        <v>74708</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3725,25 +3725,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545728</v>
+        <v>545733</v>
       </c>
       <c r="R29" t="n">
-        <v>7205466</v>
+        <v>7205544</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072477</v>
+        <v>121072470</v>
       </c>
       <c r="B30" t="n">
-        <v>74708</v>
+        <v>79711</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3837,25 +3837,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545733</v>
+        <v>545714</v>
       </c>
       <c r="R30" t="n">
-        <v>7205544</v>
+        <v>7205452</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,10 +3937,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072470</v>
+        <v>121072462</v>
       </c>
       <c r="B31" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,25 +3949,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545714</v>
+        <v>545722</v>
       </c>
       <c r="R31" t="n">
-        <v>7205452</v>
+        <v>7205383</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,10 +4049,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072462</v>
+        <v>121072476</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,25 +4061,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545722</v>
+        <v>545729</v>
       </c>
       <c r="R32" t="n">
-        <v>7205383</v>
+        <v>7205541</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 40958-2024 artfynd.xlsx
+++ b/artfynd/A 40958-2024 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072468</v>
+        <v>121072475</v>
       </c>
       <c r="B8" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,20 +1359,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545731</v>
+        <v>545745</v>
       </c>
       <c r="R8" t="n">
-        <v>7205418</v>
+        <v>7205479</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072475</v>
+        <v>121072466</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545745</v>
+        <v>545730</v>
       </c>
       <c r="R9" t="n">
-        <v>7205479</v>
+        <v>7205418</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072466</v>
+        <v>121072468</v>
       </c>
       <c r="B10" t="n">
-        <v>79683</v>
+        <v>79717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545730</v>
+        <v>545731</v>
       </c>
       <c r="R10" t="n">
         <v>7205418</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072449</v>
+        <v>121072479</v>
       </c>
       <c r="B11" t="n">
-        <v>56555</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,43 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545556</v>
+        <v>545732</v>
       </c>
       <c r="R11" t="n">
-        <v>7205352</v>
+        <v>7205572</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072479</v>
+        <v>121072449</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,34 +1811,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545732</v>
+        <v>545556</v>
       </c>
       <c r="R12" t="n">
-        <v>7205572</v>
+        <v>7205352</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 40958-2024 artfynd.xlsx
+++ b/artfynd/A 40958-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072460</v>
+        <v>121072469</v>
       </c>
       <c r="B2" t="n">
         <v>78601</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545707</v>
+        <v>545736</v>
       </c>
       <c r="R2" t="n">
-        <v>7205394</v>
+        <v>7205415</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072464</v>
+        <v>121072465</v>
       </c>
       <c r="B3" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545721</v>
+        <v>545720</v>
       </c>
       <c r="R3" t="n">
         <v>7205402</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072465</v>
+        <v>121072479</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545720</v>
+        <v>545732</v>
       </c>
       <c r="R4" t="n">
-        <v>7205402</v>
+        <v>7205572</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072459</v>
+        <v>121072476</v>
       </c>
       <c r="B5" t="n">
-        <v>79683</v>
+        <v>94484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545707</v>
+        <v>545729</v>
       </c>
       <c r="R5" t="n">
-        <v>7205394</v>
+        <v>7205541</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072455</v>
+        <v>121072472</v>
       </c>
       <c r="B6" t="n">
-        <v>79718</v>
+        <v>79711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545690</v>
+        <v>545728</v>
       </c>
       <c r="R6" t="n">
-        <v>7205351</v>
+        <v>7205466</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072469</v>
+        <v>121072454</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545736</v>
+        <v>545691</v>
       </c>
       <c r="R7" t="n">
-        <v>7205415</v>
+        <v>7205351</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072475</v>
+        <v>121072478</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545745</v>
+        <v>545728</v>
       </c>
       <c r="R8" t="n">
-        <v>7205479</v>
+        <v>7205539</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072466</v>
+        <v>121072461</v>
       </c>
       <c r="B9" t="n">
         <v>79683</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545730</v>
+        <v>545722</v>
       </c>
       <c r="R9" t="n">
-        <v>7205418</v>
+        <v>7205383</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072468</v>
+        <v>121072453</v>
       </c>
       <c r="B10" t="n">
-        <v>79717</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,38 +1583,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545731</v>
+        <v>545621</v>
       </c>
       <c r="R10" t="n">
-        <v>7205418</v>
+        <v>7205295</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072479</v>
+        <v>121072448</v>
       </c>
       <c r="B11" t="n">
         <v>78601</v>
@@ -1723,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545732</v>
+        <v>545544</v>
       </c>
       <c r="R11" t="n">
-        <v>7205572</v>
+        <v>7205290</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072449</v>
+        <v>121072475</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,43 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545556</v>
+        <v>545745</v>
       </c>
       <c r="R12" t="n">
-        <v>7205352</v>
+        <v>7205479</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072463</v>
+        <v>121072452</v>
       </c>
       <c r="B13" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,25 +1924,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545721</v>
+        <v>545599</v>
       </c>
       <c r="R13" t="n">
-        <v>7205404</v>
+        <v>7205293</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072473</v>
+        <v>121072456</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2068,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545728</v>
+        <v>545699</v>
       </c>
       <c r="R14" t="n">
-        <v>7205466</v>
+        <v>7205364</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072458</v>
+        <v>121072462</v>
       </c>
       <c r="B15" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545708</v>
+        <v>545722</v>
       </c>
       <c r="R15" t="n">
-        <v>7205391</v>
+        <v>7205383</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072471</v>
+        <v>121072473</v>
       </c>
       <c r="B16" t="n">
         <v>78601</v>
@@ -2292,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545706</v>
+        <v>545728</v>
       </c>
       <c r="R16" t="n">
-        <v>7205465</v>
+        <v>7205466</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072448</v>
+        <v>121072464</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545544</v>
+        <v>545721</v>
       </c>
       <c r="R17" t="n">
-        <v>7205290</v>
+        <v>7205402</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,7 +2472,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072456</v>
+        <v>121072457</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2516,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545699</v>
+        <v>545695</v>
       </c>
       <c r="R18" t="n">
-        <v>7205364</v>
+        <v>7205372</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,7 +2584,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072447</v>
+        <v>121072459</v>
       </c>
       <c r="B19" t="n">
         <v>79683</v>
@@ -2628,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545544</v>
+        <v>545707</v>
       </c>
       <c r="R19" t="n">
-        <v>7205293</v>
+        <v>7205394</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072474</v>
+        <v>121072447</v>
       </c>
       <c r="B20" t="n">
-        <v>90711</v>
+        <v>79683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545747</v>
+        <v>545544</v>
       </c>
       <c r="R20" t="n">
-        <v>7205478</v>
+        <v>7205293</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072467</v>
+        <v>121072455</v>
       </c>
       <c r="B21" t="n">
-        <v>79711</v>
+        <v>79718</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,21 +2824,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545730</v>
+        <v>545690</v>
       </c>
       <c r="R21" t="n">
-        <v>7205418</v>
+        <v>7205351</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072478</v>
+        <v>121072458</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2932,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545728</v>
+        <v>545708</v>
       </c>
       <c r="R22" t="n">
-        <v>7205539</v>
+        <v>7205391</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072453</v>
+        <v>121072466</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>79683</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,39 +3048,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545621</v>
+        <v>545730</v>
       </c>
       <c r="R23" t="n">
-        <v>7205295</v>
+        <v>7205418</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072451</v>
+        <v>121072463</v>
       </c>
       <c r="B24" t="n">
-        <v>79683</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,25 +3156,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545599</v>
+        <v>545721</v>
       </c>
       <c r="R24" t="n">
-        <v>7205293</v>
+        <v>7205404</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072454</v>
+        <v>121072474</v>
       </c>
       <c r="B25" t="n">
-        <v>79683</v>
+        <v>90711</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,21 +3272,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545691</v>
+        <v>545747</v>
       </c>
       <c r="R25" t="n">
-        <v>7205351</v>
+        <v>7205478</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,7 +3368,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072457</v>
+        <v>121072460</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3417,10 +3408,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545695</v>
+        <v>545707</v>
       </c>
       <c r="R26" t="n">
-        <v>7205372</v>
+        <v>7205394</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072461</v>
+        <v>121072477</v>
       </c>
       <c r="B27" t="n">
-        <v>79683</v>
+        <v>74708</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,21 +3496,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545722</v>
+        <v>545733</v>
       </c>
       <c r="R27" t="n">
-        <v>7205383</v>
+        <v>7205544</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3565,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072472</v>
+        <v>121072468</v>
       </c>
       <c r="B28" t="n">
-        <v>79711</v>
+        <v>79717</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,21 +3608,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545728</v>
+        <v>545731</v>
       </c>
       <c r="R28" t="n">
-        <v>7205466</v>
+        <v>7205418</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072477</v>
+        <v>121072451</v>
       </c>
       <c r="B29" t="n">
-        <v>74708</v>
+        <v>79683</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,21 +3720,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3753,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545733</v>
+        <v>545599</v>
       </c>
       <c r="R29" t="n">
-        <v>7205544</v>
+        <v>7205293</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3788,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3798,7 +3789,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072470</v>
+        <v>121072471</v>
       </c>
       <c r="B30" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3837,25 +3828,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545714</v>
+        <v>545706</v>
       </c>
       <c r="R30" t="n">
-        <v>7205452</v>
+        <v>7205465</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3937,10 +3928,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072462</v>
+        <v>121072467</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,25 +3940,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3977,10 +3968,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545722</v>
+        <v>545730</v>
       </c>
       <c r="R31" t="n">
-        <v>7205383</v>
+        <v>7205418</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4012,7 +4003,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4022,7 +4013,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072476</v>
+        <v>121072470</v>
       </c>
       <c r="B32" t="n">
-        <v>94484</v>
+        <v>79711</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4065,21 +4056,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4089,10 +4080,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545729</v>
+        <v>545714</v>
       </c>
       <c r="R32" t="n">
-        <v>7205541</v>
+        <v>7205452</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4124,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4134,7 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4161,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072452</v>
+        <v>121072449</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>56555</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4177,34 +4168,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545599</v>
+        <v>545556</v>
       </c>
       <c r="R33" t="n">
-        <v>7205293</v>
+        <v>7205352</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 40958-2024 artfynd.xlsx
+++ b/artfynd/A 40958-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072469</v>
+        <v>121072477</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>74710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545736</v>
+        <v>545733</v>
       </c>
       <c r="R2" t="n">
-        <v>7205415</v>
+        <v>7205544</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072465</v>
+        <v>121072461</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545720</v>
+        <v>545722</v>
       </c>
       <c r="R3" t="n">
-        <v>7205402</v>
+        <v>7205383</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072479</v>
+        <v>121072473</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545732</v>
+        <v>545728</v>
       </c>
       <c r="R4" t="n">
-        <v>7205572</v>
+        <v>7205466</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072476</v>
+        <v>121072469</v>
       </c>
       <c r="B5" t="n">
-        <v>94484</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545729</v>
+        <v>545736</v>
       </c>
       <c r="R5" t="n">
-        <v>7205541</v>
+        <v>7205415</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072472</v>
+        <v>121072470</v>
       </c>
       <c r="B6" t="n">
-        <v>79711</v>
+        <v>79714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545728</v>
+        <v>545714</v>
       </c>
       <c r="R6" t="n">
-        <v>7205466</v>
+        <v>7205452</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072454</v>
+        <v>121072475</v>
       </c>
       <c r="B7" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545691</v>
+        <v>545745</v>
       </c>
       <c r="R7" t="n">
-        <v>7205351</v>
+        <v>7205479</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072478</v>
+        <v>121072456</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545728</v>
+        <v>545699</v>
       </c>
       <c r="R8" t="n">
-        <v>7205539</v>
+        <v>7205364</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072461</v>
+        <v>121072458</v>
       </c>
       <c r="B9" t="n">
-        <v>79683</v>
+        <v>79721</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545722</v>
+        <v>545708</v>
       </c>
       <c r="R9" t="n">
-        <v>7205383</v>
+        <v>7205391</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072453</v>
+        <v>121072476</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>94496</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,43 +1583,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545621</v>
+        <v>545729</v>
       </c>
       <c r="R10" t="n">
-        <v>7205295</v>
+        <v>7205541</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072448</v>
+        <v>121072468</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,20 +1695,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545544</v>
+        <v>545731</v>
       </c>
       <c r="R11" t="n">
-        <v>7205290</v>
+        <v>7205418</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072475</v>
+        <v>121072459</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545745</v>
+        <v>545707</v>
       </c>
       <c r="R12" t="n">
-        <v>7205479</v>
+        <v>7205394</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072452</v>
+        <v>121072464</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545599</v>
+        <v>545721</v>
       </c>
       <c r="R13" t="n">
-        <v>7205293</v>
+        <v>7205402</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072456</v>
+        <v>121072465</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545699</v>
+        <v>545720</v>
       </c>
       <c r="R14" t="n">
-        <v>7205364</v>
+        <v>7205402</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072462</v>
+        <v>121072471</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545722</v>
+        <v>545706</v>
       </c>
       <c r="R15" t="n">
-        <v>7205383</v>
+        <v>7205465</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072473</v>
+        <v>121072453</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,34 +2259,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545728</v>
+        <v>545621</v>
       </c>
       <c r="R16" t="n">
-        <v>7205466</v>
+        <v>7205295</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072464</v>
+        <v>121072455</v>
       </c>
       <c r="B17" t="n">
-        <v>79683</v>
+        <v>79721</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545721</v>
+        <v>545690</v>
       </c>
       <c r="R17" t="n">
-        <v>7205402</v>
+        <v>7205351</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072457</v>
+        <v>121072454</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545695</v>
+        <v>545691</v>
       </c>
       <c r="R18" t="n">
-        <v>7205372</v>
+        <v>7205351</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072459</v>
+        <v>121072474</v>
       </c>
       <c r="B19" t="n">
-        <v>79683</v>
+        <v>90723</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545707</v>
+        <v>545747</v>
       </c>
       <c r="R19" t="n">
-        <v>7205394</v>
+        <v>7205478</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072447</v>
+        <v>121072460</v>
       </c>
       <c r="B20" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545544</v>
+        <v>545707</v>
       </c>
       <c r="R20" t="n">
-        <v>7205293</v>
+        <v>7205394</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072455</v>
+        <v>121072479</v>
       </c>
       <c r="B21" t="n">
-        <v>79718</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545690</v>
+        <v>545732</v>
       </c>
       <c r="R21" t="n">
-        <v>7205351</v>
+        <v>7205572</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072458</v>
+        <v>121072463</v>
       </c>
       <c r="B22" t="n">
-        <v>79718</v>
+        <v>79721</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545708</v>
+        <v>545721</v>
       </c>
       <c r="R22" t="n">
-        <v>7205391</v>
+        <v>7205404</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072466</v>
+        <v>121072472</v>
       </c>
       <c r="B23" t="n">
-        <v>79683</v>
+        <v>79714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545730</v>
+        <v>545728</v>
       </c>
       <c r="R23" t="n">
-        <v>7205418</v>
+        <v>7205466</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072463</v>
+        <v>121072452</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,25 +3156,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545721</v>
+        <v>545599</v>
       </c>
       <c r="R24" t="n">
-        <v>7205404</v>
+        <v>7205293</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072474</v>
+        <v>121072478</v>
       </c>
       <c r="B25" t="n">
-        <v>90711</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545747</v>
+        <v>545728</v>
       </c>
       <c r="R25" t="n">
-        <v>7205478</v>
+        <v>7205539</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072460</v>
+        <v>121072448</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545707</v>
+        <v>545544</v>
       </c>
       <c r="R26" t="n">
-        <v>7205394</v>
+        <v>7205290</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072477</v>
+        <v>121072457</v>
       </c>
       <c r="B27" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,21 +3496,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545733</v>
+        <v>545695</v>
       </c>
       <c r="R27" t="n">
-        <v>7205544</v>
+        <v>7205372</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072468</v>
+        <v>121072462</v>
       </c>
       <c r="B28" t="n">
-        <v>79717</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3604,20 +3604,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545731</v>
+        <v>545722</v>
       </c>
       <c r="R28" t="n">
-        <v>7205418</v>
+        <v>7205383</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072451</v>
+        <v>121072449</v>
       </c>
       <c r="B29" t="n">
-        <v>79683</v>
+        <v>56555</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,34 +3720,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545599</v>
+        <v>545556</v>
       </c>
       <c r="R29" t="n">
-        <v>7205293</v>
+        <v>7205352</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,7 +3788,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3798,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072471</v>
+        <v>121072467</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3828,25 +3837,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3856,10 +3865,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545706</v>
+        <v>545730</v>
       </c>
       <c r="R30" t="n">
-        <v>7205465</v>
+        <v>7205418</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3891,7 +3900,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3910,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,10 +3937,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072467</v>
+        <v>121072447</v>
       </c>
       <c r="B31" t="n">
-        <v>79711</v>
+        <v>79686</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3940,25 +3949,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545730</v>
+        <v>545544</v>
       </c>
       <c r="R31" t="n">
-        <v>7205418</v>
+        <v>7205293</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4003,7 +4012,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +4022,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,10 +4049,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072470</v>
+        <v>121072451</v>
       </c>
       <c r="B32" t="n">
-        <v>79711</v>
+        <v>79686</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4052,25 +4061,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +4089,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545714</v>
+        <v>545599</v>
       </c>
       <c r="R32" t="n">
-        <v>7205452</v>
+        <v>7205293</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4115,7 +4124,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4134,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,10 +4161,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072449</v>
+        <v>121072466</v>
       </c>
       <c r="B33" t="n">
-        <v>56555</v>
+        <v>79686</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,43 +4177,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545556</v>
+        <v>545730</v>
       </c>
       <c r="R33" t="n">
-        <v>7205352</v>
+        <v>7205418</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
